--- a/data/istanbul/service_status.xlsx
+++ b/data/istanbul/service_status.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,6 +458,296 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2026-04-06 10:59:06</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>ftekin</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1002</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2026-04-06 10:59:06</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>ftekin</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1003</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2026-04-06 10:59:06</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>ftekin</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1004</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2026-04-06 10:59:06</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>ftekin</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1005</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2026-04-06 10:59:06</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>ftekin</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1006</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2026-04-06 10:59:06</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>ftekin</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1007</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2026-04-06 10:59:06</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>ftekin</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1008</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2026-04-06 10:59:06</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>ftekin</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1009</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2026-04-06 10:59:06</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>ftekin</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
